--- a/automation/reports/Excel/Selenium_Automation_Test_Report.xlsx
+++ b/automation/reports/Excel/Selenium_Automation_Test_Report.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3068" uniqueCount="640">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3068" uniqueCount="639">
   <si>
     <t>Test ID</t>
   </si>
@@ -1920,9 +1920,6 @@
   </si>
   <si>
     <t>Total Duration (ms)</t>
-  </si>
-  <si>
-    <t>4870</t>
   </si>
   <si>
     <t>Defect ID</t>
@@ -2049,7 +2046,7 @@
         <v>10</v>
       </c>
       <c r="F2" t="n" s="0">
-        <v>30.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="3">
@@ -2069,7 +2066,7 @@
         <v>10</v>
       </c>
       <c r="F3" t="n" s="0">
-        <v>14.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="4">
@@ -2089,7 +2086,7 @@
         <v>10</v>
       </c>
       <c r="F4" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="5">
@@ -2109,7 +2106,7 @@
         <v>10</v>
       </c>
       <c r="F5" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="6">
@@ -2129,7 +2126,7 @@
         <v>10</v>
       </c>
       <c r="F6" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="7">
@@ -2149,7 +2146,7 @@
         <v>10</v>
       </c>
       <c r="F7" t="n" s="0">
-        <v>14.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="8">
@@ -2169,7 +2166,7 @@
         <v>10</v>
       </c>
       <c r="F8" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="9">
@@ -2189,7 +2186,7 @@
         <v>10</v>
       </c>
       <c r="F9" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="10">
@@ -2209,7 +2206,7 @@
         <v>10</v>
       </c>
       <c r="F10" t="n" s="0">
-        <v>20.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="11">
@@ -2229,7 +2226,7 @@
         <v>10</v>
       </c>
       <c r="F11" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="12">
@@ -2249,7 +2246,7 @@
         <v>10</v>
       </c>
       <c r="F12" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="13">
@@ -2269,7 +2266,7 @@
         <v>10</v>
       </c>
       <c r="F13" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="14">
@@ -2289,7 +2286,7 @@
         <v>10</v>
       </c>
       <c r="F14" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="15">
@@ -2309,7 +2306,7 @@
         <v>10</v>
       </c>
       <c r="F15" t="n" s="0">
-        <v>14.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="16">
@@ -2329,7 +2326,7 @@
         <v>10</v>
       </c>
       <c r="F16" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="17">
@@ -2349,7 +2346,7 @@
         <v>10</v>
       </c>
       <c r="F17" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="18">
@@ -2369,7 +2366,7 @@
         <v>10</v>
       </c>
       <c r="F18" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="19">
@@ -2389,7 +2386,7 @@
         <v>10</v>
       </c>
       <c r="F19" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="20">
@@ -2409,7 +2406,7 @@
         <v>10</v>
       </c>
       <c r="F20" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="21">
@@ -2429,7 +2426,7 @@
         <v>10</v>
       </c>
       <c r="F21" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="22">
@@ -2449,7 +2446,7 @@
         <v>10</v>
       </c>
       <c r="F22" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="23">
@@ -2469,7 +2466,7 @@
         <v>10</v>
       </c>
       <c r="F23" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="24">
@@ -2489,7 +2486,7 @@
         <v>10</v>
       </c>
       <c r="F24" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="25">
@@ -2509,7 +2506,7 @@
         <v>10</v>
       </c>
       <c r="F25" t="n" s="0">
-        <v>11.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="26">
@@ -2529,7 +2526,7 @@
         <v>10</v>
       </c>
       <c r="F26" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="27">
@@ -2549,7 +2546,7 @@
         <v>10</v>
       </c>
       <c r="F27" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="28">
@@ -2569,7 +2566,7 @@
         <v>10</v>
       </c>
       <c r="F28" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="29">
@@ -2589,7 +2586,7 @@
         <v>10</v>
       </c>
       <c r="F29" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="30">
@@ -2609,7 +2606,7 @@
         <v>10</v>
       </c>
       <c r="F30" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="31">
@@ -2629,7 +2626,7 @@
         <v>10</v>
       </c>
       <c r="F31" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="32">
@@ -2649,7 +2646,7 @@
         <v>10</v>
       </c>
       <c r="F32" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="33">
@@ -2669,7 +2666,7 @@
         <v>10</v>
       </c>
       <c r="F33" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="34">
@@ -2689,7 +2686,7 @@
         <v>10</v>
       </c>
       <c r="F34" t="n" s="0">
-        <v>14.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="35">
@@ -2709,7 +2706,7 @@
         <v>10</v>
       </c>
       <c r="F35" t="n" s="0">
-        <v>14.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="36">
@@ -2729,7 +2726,7 @@
         <v>10</v>
       </c>
       <c r="F36" t="n" s="0">
-        <v>14.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="37">
@@ -2749,7 +2746,7 @@
         <v>10</v>
       </c>
       <c r="F37" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="38">
@@ -2769,7 +2766,7 @@
         <v>10</v>
       </c>
       <c r="F38" t="n" s="0">
-        <v>14.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="39">
@@ -2789,7 +2786,7 @@
         <v>10</v>
       </c>
       <c r="F39" t="n" s="0">
-        <v>14.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="40">
@@ -2809,7 +2806,7 @@
         <v>10</v>
       </c>
       <c r="F40" t="n" s="0">
-        <v>21.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="41">
@@ -2829,7 +2826,7 @@
         <v>10</v>
       </c>
       <c r="F41" t="n" s="0">
-        <v>26.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="42">
@@ -2849,7 +2846,7 @@
         <v>10</v>
       </c>
       <c r="F42" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="43">
@@ -2869,7 +2866,7 @@
         <v>10</v>
       </c>
       <c r="F43" t="n" s="0">
-        <v>18.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="44">
@@ -2889,7 +2886,7 @@
         <v>10</v>
       </c>
       <c r="F44" t="n" s="0">
-        <v>21.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="45">
@@ -2909,7 +2906,7 @@
         <v>10</v>
       </c>
       <c r="F45" t="n" s="0">
-        <v>25.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="46">
@@ -2929,7 +2926,7 @@
         <v>10</v>
       </c>
       <c r="F46" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="47">
@@ -2949,7 +2946,7 @@
         <v>10</v>
       </c>
       <c r="F47" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="48">
@@ -2969,7 +2966,7 @@
         <v>10</v>
       </c>
       <c r="F48" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="49">
@@ -2989,7 +2986,7 @@
         <v>10</v>
       </c>
       <c r="F49" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="50">
@@ -3009,7 +3006,7 @@
         <v>10</v>
       </c>
       <c r="F50" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="51">
@@ -3029,7 +3026,7 @@
         <v>10</v>
       </c>
       <c r="F51" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="52">
@@ -3049,7 +3046,7 @@
         <v>10</v>
       </c>
       <c r="F52" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="53">
@@ -3069,7 +3066,7 @@
         <v>10</v>
       </c>
       <c r="F53" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="54">
@@ -3089,7 +3086,7 @@
         <v>10</v>
       </c>
       <c r="F54" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="55">
@@ -3109,7 +3106,7 @@
         <v>10</v>
       </c>
       <c r="F55" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="56">
@@ -3129,7 +3126,7 @@
         <v>10</v>
       </c>
       <c r="F56" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="57">
@@ -3149,7 +3146,7 @@
         <v>10</v>
       </c>
       <c r="F57" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="58">
@@ -3169,7 +3166,7 @@
         <v>10</v>
       </c>
       <c r="F58" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="59">
@@ -3189,7 +3186,7 @@
         <v>10</v>
       </c>
       <c r="F59" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="60">
@@ -3209,7 +3206,7 @@
         <v>10</v>
       </c>
       <c r="F60" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="61">
@@ -3229,7 +3226,7 @@
         <v>10</v>
       </c>
       <c r="F61" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="62">
@@ -3249,7 +3246,7 @@
         <v>10</v>
       </c>
       <c r="F62" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="63">
@@ -3269,7 +3266,7 @@
         <v>10</v>
       </c>
       <c r="F63" t="n" s="0">
-        <v>19.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="64">
@@ -3289,7 +3286,7 @@
         <v>10</v>
       </c>
       <c r="F64" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="65">
@@ -3309,7 +3306,7 @@
         <v>10</v>
       </c>
       <c r="F65" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="66">
@@ -3329,7 +3326,7 @@
         <v>10</v>
       </c>
       <c r="F66" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="67">
@@ -3349,7 +3346,7 @@
         <v>10</v>
       </c>
       <c r="F67" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="68">
@@ -3369,7 +3366,7 @@
         <v>10</v>
       </c>
       <c r="F68" t="n" s="0">
-        <v>23.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="69">
@@ -3389,7 +3386,7 @@
         <v>10</v>
       </c>
       <c r="F69" t="n" s="0">
-        <v>12.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="70">
@@ -3409,7 +3406,7 @@
         <v>10</v>
       </c>
       <c r="F70" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="71">
@@ -3429,7 +3426,7 @@
         <v>10</v>
       </c>
       <c r="F71" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="72">
@@ -3449,7 +3446,7 @@
         <v>10</v>
       </c>
       <c r="F72" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="73">
@@ -3469,7 +3466,7 @@
         <v>10</v>
       </c>
       <c r="F73" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="74">
@@ -3489,7 +3486,7 @@
         <v>10</v>
       </c>
       <c r="F74" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="75">
@@ -3509,7 +3506,7 @@
         <v>10</v>
       </c>
       <c r="F75" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="76">
@@ -3529,7 +3526,7 @@
         <v>10</v>
       </c>
       <c r="F76" t="n" s="0">
-        <v>14.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="77">
@@ -3549,7 +3546,7 @@
         <v>10</v>
       </c>
       <c r="F77" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="78">
@@ -3569,7 +3566,7 @@
         <v>10</v>
       </c>
       <c r="F78" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="79">
@@ -3589,7 +3586,7 @@
         <v>10</v>
       </c>
       <c r="F79" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="80">
@@ -3609,7 +3606,7 @@
         <v>10</v>
       </c>
       <c r="F80" t="n" s="0">
-        <v>19.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="81">
@@ -3629,7 +3626,7 @@
         <v>10</v>
       </c>
       <c r="F81" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="82">
@@ -3649,7 +3646,7 @@
         <v>10</v>
       </c>
       <c r="F82" t="n" s="0">
-        <v>19.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="83">
@@ -3669,7 +3666,7 @@
         <v>10</v>
       </c>
       <c r="F83" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="84">
@@ -3689,7 +3686,7 @@
         <v>10</v>
       </c>
       <c r="F84" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="85">
@@ -3709,7 +3706,7 @@
         <v>10</v>
       </c>
       <c r="F85" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="86">
@@ -3729,7 +3726,7 @@
         <v>10</v>
       </c>
       <c r="F86" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="87">
@@ -3749,7 +3746,7 @@
         <v>10</v>
       </c>
       <c r="F87" t="n" s="0">
-        <v>18.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="88">
@@ -3769,7 +3766,7 @@
         <v>10</v>
       </c>
       <c r="F88" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="89">
@@ -3789,7 +3786,7 @@
         <v>10</v>
       </c>
       <c r="F89" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="90">
@@ -3809,7 +3806,7 @@
         <v>10</v>
       </c>
       <c r="F90" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="91">
@@ -3829,7 +3826,7 @@
         <v>10</v>
       </c>
       <c r="F91" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="92">
@@ -3849,7 +3846,7 @@
         <v>10</v>
       </c>
       <c r="F92" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="93">
@@ -3869,7 +3866,7 @@
         <v>10</v>
       </c>
       <c r="F93" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="94">
@@ -3889,7 +3886,7 @@
         <v>10</v>
       </c>
       <c r="F94" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="95">
@@ -3909,7 +3906,7 @@
         <v>10</v>
       </c>
       <c r="F95" t="n" s="0">
-        <v>19.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="96">
@@ -3929,7 +3926,7 @@
         <v>10</v>
       </c>
       <c r="F96" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="97">
@@ -3949,7 +3946,7 @@
         <v>10</v>
       </c>
       <c r="F97" t="n" s="0">
-        <v>14.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="98">
@@ -3969,7 +3966,7 @@
         <v>10</v>
       </c>
       <c r="F98" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="99">
@@ -3989,7 +3986,7 @@
         <v>10</v>
       </c>
       <c r="F99" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="100">
@@ -4009,7 +4006,7 @@
         <v>10</v>
       </c>
       <c r="F100" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="101">
@@ -4029,7 +4026,7 @@
         <v>10</v>
       </c>
       <c r="F101" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="102">
@@ -4049,7 +4046,7 @@
         <v>10</v>
       </c>
       <c r="F102" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="103">
@@ -4069,7 +4066,7 @@
         <v>10</v>
       </c>
       <c r="F103" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="104">
@@ -4089,7 +4086,7 @@
         <v>10</v>
       </c>
       <c r="F104" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="105">
@@ -4109,7 +4106,7 @@
         <v>10</v>
       </c>
       <c r="F105" t="n" s="0">
-        <v>18.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="106">
@@ -4129,7 +4126,7 @@
         <v>10</v>
       </c>
       <c r="F106" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="107">
@@ -4149,7 +4146,7 @@
         <v>10</v>
       </c>
       <c r="F107" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="108">
@@ -4169,7 +4166,7 @@
         <v>10</v>
       </c>
       <c r="F108" t="n" s="0">
-        <v>14.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="109">
@@ -4189,7 +4186,7 @@
         <v>10</v>
       </c>
       <c r="F109" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="110">
@@ -4209,7 +4206,7 @@
         <v>10</v>
       </c>
       <c r="F110" t="n" s="0">
-        <v>19.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="111">
@@ -4229,7 +4226,7 @@
         <v>10</v>
       </c>
       <c r="F111" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="112">
@@ -4249,7 +4246,7 @@
         <v>10</v>
       </c>
       <c r="F112" t="n" s="0">
-        <v>14.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="113">
@@ -4269,7 +4266,7 @@
         <v>10</v>
       </c>
       <c r="F113" t="n" s="0">
-        <v>18.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="114">
@@ -4289,7 +4286,7 @@
         <v>10</v>
       </c>
       <c r="F114" t="n" s="0">
-        <v>14.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="115">
@@ -4309,7 +4306,7 @@
         <v>10</v>
       </c>
       <c r="F115" t="n" s="0">
-        <v>18.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="116">
@@ -4329,7 +4326,7 @@
         <v>10</v>
       </c>
       <c r="F116" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="117">
@@ -4349,7 +4346,7 @@
         <v>10</v>
       </c>
       <c r="F117" t="n" s="0">
-        <v>18.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="118">
@@ -4369,7 +4366,7 @@
         <v>10</v>
       </c>
       <c r="F118" t="n" s="0">
-        <v>14.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="119">
@@ -4389,7 +4386,7 @@
         <v>10</v>
       </c>
       <c r="F119" t="n" s="0">
-        <v>18.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="120">
@@ -4409,7 +4406,7 @@
         <v>10</v>
       </c>
       <c r="F120" t="n" s="0">
-        <v>14.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="121">
@@ -4429,7 +4426,7 @@
         <v>10</v>
       </c>
       <c r="F121" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="122">
@@ -4449,7 +4446,7 @@
         <v>10</v>
       </c>
       <c r="F122" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="123">
@@ -4469,7 +4466,7 @@
         <v>10</v>
       </c>
       <c r="F123" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="124">
@@ -4489,7 +4486,7 @@
         <v>10</v>
       </c>
       <c r="F124" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="125">
@@ -4509,7 +4506,7 @@
         <v>10</v>
       </c>
       <c r="F125" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="126">
@@ -4529,7 +4526,7 @@
         <v>10</v>
       </c>
       <c r="F126" t="n" s="0">
-        <v>13.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="127">
@@ -4549,7 +4546,7 @@
         <v>10</v>
       </c>
       <c r="F127" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="128">
@@ -4569,7 +4566,7 @@
         <v>10</v>
       </c>
       <c r="F128" t="n" s="0">
-        <v>18.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="129">
@@ -4589,7 +4586,7 @@
         <v>10</v>
       </c>
       <c r="F129" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="130">
@@ -4609,7 +4606,7 @@
         <v>10</v>
       </c>
       <c r="F130" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="131">
@@ -4629,7 +4626,7 @@
         <v>10</v>
       </c>
       <c r="F131" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="132">
@@ -4649,7 +4646,7 @@
         <v>10</v>
       </c>
       <c r="F132" t="n" s="0">
-        <v>14.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="133">
@@ -4669,7 +4666,7 @@
         <v>10</v>
       </c>
       <c r="F133" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="134">
@@ -4689,7 +4686,7 @@
         <v>10</v>
       </c>
       <c r="F134" t="n" s="0">
-        <v>14.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="135">
@@ -4709,7 +4706,7 @@
         <v>10</v>
       </c>
       <c r="F135" t="n" s="0">
-        <v>19.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="136">
@@ -4729,7 +4726,7 @@
         <v>10</v>
       </c>
       <c r="F136" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="137">
@@ -4749,7 +4746,7 @@
         <v>10</v>
       </c>
       <c r="F137" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="138">
@@ -4769,7 +4766,7 @@
         <v>10</v>
       </c>
       <c r="F138" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="139">
@@ -4789,7 +4786,7 @@
         <v>10</v>
       </c>
       <c r="F139" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="140">
@@ -4809,7 +4806,7 @@
         <v>10</v>
       </c>
       <c r="F140" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="141">
@@ -4829,7 +4826,7 @@
         <v>10</v>
       </c>
       <c r="F141" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="142">
@@ -4849,7 +4846,7 @@
         <v>10</v>
       </c>
       <c r="F142" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="143">
@@ -4869,7 +4866,7 @@
         <v>10</v>
       </c>
       <c r="F143" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="144">
@@ -4889,7 +4886,7 @@
         <v>10</v>
       </c>
       <c r="F144" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="145">
@@ -4909,7 +4906,7 @@
         <v>10</v>
       </c>
       <c r="F145" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="146">
@@ -4929,7 +4926,7 @@
         <v>10</v>
       </c>
       <c r="F146" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="147">
@@ -4949,7 +4946,7 @@
         <v>10</v>
       </c>
       <c r="F147" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="148">
@@ -4969,7 +4966,7 @@
         <v>10</v>
       </c>
       <c r="F148" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="149">
@@ -4989,7 +4986,7 @@
         <v>10</v>
       </c>
       <c r="F149" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="150">
@@ -5009,7 +5006,7 @@
         <v>10</v>
       </c>
       <c r="F150" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="151">
@@ -5029,7 +5026,7 @@
         <v>10</v>
       </c>
       <c r="F151" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="152">
@@ -5049,7 +5046,7 @@
         <v>10</v>
       </c>
       <c r="F152" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="153">
@@ -5069,7 +5066,7 @@
         <v>10</v>
       </c>
       <c r="F153" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="154">
@@ -5089,7 +5086,7 @@
         <v>10</v>
       </c>
       <c r="F154" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="155">
@@ -5109,7 +5106,7 @@
         <v>10</v>
       </c>
       <c r="F155" t="n" s="0">
-        <v>18.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="156">
@@ -5129,7 +5126,7 @@
         <v>10</v>
       </c>
       <c r="F156" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="157">
@@ -5149,7 +5146,7 @@
         <v>10</v>
       </c>
       <c r="F157" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="158">
@@ -5169,7 +5166,7 @@
         <v>10</v>
       </c>
       <c r="F158" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="159">
@@ -5189,7 +5186,7 @@
         <v>10</v>
       </c>
       <c r="F159" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="160">
@@ -5209,7 +5206,7 @@
         <v>10</v>
       </c>
       <c r="F160" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="161">
@@ -5229,7 +5226,7 @@
         <v>10</v>
       </c>
       <c r="F161" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="162">
@@ -5249,7 +5246,7 @@
         <v>10</v>
       </c>
       <c r="F162" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="163">
@@ -5269,7 +5266,7 @@
         <v>10</v>
       </c>
       <c r="F163" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="164">
@@ -5289,7 +5286,7 @@
         <v>10</v>
       </c>
       <c r="F164" t="n" s="0">
-        <v>19.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="165">
@@ -5309,7 +5306,7 @@
         <v>10</v>
       </c>
       <c r="F165" t="n" s="0">
-        <v>14.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="166">
@@ -5329,7 +5326,7 @@
         <v>10</v>
       </c>
       <c r="F166" t="n" s="0">
-        <v>19.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="167">
@@ -5349,7 +5346,7 @@
         <v>10</v>
       </c>
       <c r="F167" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="168">
@@ -5369,7 +5366,7 @@
         <v>10</v>
       </c>
       <c r="F168" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="169">
@@ -5389,7 +5386,7 @@
         <v>10</v>
       </c>
       <c r="F169" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="170">
@@ -5409,7 +5406,7 @@
         <v>10</v>
       </c>
       <c r="F170" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="171">
@@ -5429,7 +5426,7 @@
         <v>10</v>
       </c>
       <c r="F171" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="172">
@@ -5449,7 +5446,7 @@
         <v>10</v>
       </c>
       <c r="F172" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="173">
@@ -5469,7 +5466,7 @@
         <v>10</v>
       </c>
       <c r="F173" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="174">
@@ -5489,7 +5486,7 @@
         <v>10</v>
       </c>
       <c r="F174" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="175">
@@ -5509,7 +5506,7 @@
         <v>10</v>
       </c>
       <c r="F175" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="176">
@@ -5529,7 +5526,7 @@
         <v>10</v>
       </c>
       <c r="F176" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="177">
@@ -5549,7 +5546,7 @@
         <v>10</v>
       </c>
       <c r="F177" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="178">
@@ -5569,7 +5566,7 @@
         <v>10</v>
       </c>
       <c r="F178" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="179">
@@ -5589,7 +5586,7 @@
         <v>10</v>
       </c>
       <c r="F179" t="n" s="0">
-        <v>18.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="180">
@@ -5609,7 +5606,7 @@
         <v>10</v>
       </c>
       <c r="F180" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="181">
@@ -5629,7 +5626,7 @@
         <v>10</v>
       </c>
       <c r="F181" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="182">
@@ -5649,7 +5646,7 @@
         <v>10</v>
       </c>
       <c r="F182" t="n" s="0">
-        <v>18.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="183">
@@ -5669,7 +5666,7 @@
         <v>10</v>
       </c>
       <c r="F183" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="184">
@@ -5689,7 +5686,7 @@
         <v>10</v>
       </c>
       <c r="F184" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="185">
@@ -5709,7 +5706,7 @@
         <v>10</v>
       </c>
       <c r="F185" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="186">
@@ -5729,7 +5726,7 @@
         <v>10</v>
       </c>
       <c r="F186" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="187">
@@ -5749,7 +5746,7 @@
         <v>10</v>
       </c>
       <c r="F187" t="n" s="0">
-        <v>18.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="188">
@@ -5769,7 +5766,7 @@
         <v>10</v>
       </c>
       <c r="F188" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="189">
@@ -5789,7 +5786,7 @@
         <v>10</v>
       </c>
       <c r="F189" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="190">
@@ -5809,7 +5806,7 @@
         <v>10</v>
       </c>
       <c r="F190" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="191">
@@ -5829,7 +5826,7 @@
         <v>10</v>
       </c>
       <c r="F191" t="n" s="0">
-        <v>18.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="192">
@@ -5849,7 +5846,7 @@
         <v>10</v>
       </c>
       <c r="F192" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="193">
@@ -5869,7 +5866,7 @@
         <v>10</v>
       </c>
       <c r="F193" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="194">
@@ -5889,7 +5886,7 @@
         <v>10</v>
       </c>
       <c r="F194" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="195">
@@ -5909,7 +5906,7 @@
         <v>10</v>
       </c>
       <c r="F195" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="196">
@@ -5929,7 +5926,7 @@
         <v>10</v>
       </c>
       <c r="F196" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="197">
@@ -5949,7 +5946,7 @@
         <v>10</v>
       </c>
       <c r="F197" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="198">
@@ -5969,7 +5966,7 @@
         <v>10</v>
       </c>
       <c r="F198" t="n" s="0">
-        <v>18.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="199">
@@ -5989,7 +5986,7 @@
         <v>10</v>
       </c>
       <c r="F199" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="200">
@@ -6009,7 +6006,7 @@
         <v>10</v>
       </c>
       <c r="F200" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="201">
@@ -6029,7 +6026,7 @@
         <v>10</v>
       </c>
       <c r="F201" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="202">
@@ -6049,7 +6046,7 @@
         <v>10</v>
       </c>
       <c r="F202" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="203">
@@ -6069,7 +6066,7 @@
         <v>10</v>
       </c>
       <c r="F203" t="n" s="0">
-        <v>18.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="204">
@@ -6089,7 +6086,7 @@
         <v>10</v>
       </c>
       <c r="F204" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="205">
@@ -6109,7 +6106,7 @@
         <v>10</v>
       </c>
       <c r="F205" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="206">
@@ -6129,7 +6126,7 @@
         <v>10</v>
       </c>
       <c r="F206" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="207">
@@ -6149,7 +6146,7 @@
         <v>10</v>
       </c>
       <c r="F207" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="208">
@@ -6169,7 +6166,7 @@
         <v>10</v>
       </c>
       <c r="F208" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="209">
@@ -6189,7 +6186,7 @@
         <v>10</v>
       </c>
       <c r="F209" t="n" s="0">
-        <v>18.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="210">
@@ -6209,7 +6206,7 @@
         <v>10</v>
       </c>
       <c r="F210" t="n" s="0">
-        <v>14.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="211">
@@ -6229,7 +6226,7 @@
         <v>10</v>
       </c>
       <c r="F211" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="212">
@@ -6249,7 +6246,7 @@
         <v>10</v>
       </c>
       <c r="F212" t="n" s="0">
-        <v>19.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="213">
@@ -6269,7 +6266,7 @@
         <v>10</v>
       </c>
       <c r="F213" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="214">
@@ -6289,7 +6286,7 @@
         <v>10</v>
       </c>
       <c r="F214" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="215">
@@ -6309,7 +6306,7 @@
         <v>10</v>
       </c>
       <c r="F215" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="216">
@@ -6329,7 +6326,7 @@
         <v>10</v>
       </c>
       <c r="F216" t="n" s="0">
-        <v>14.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="217">
@@ -6349,7 +6346,7 @@
         <v>10</v>
       </c>
       <c r="F217" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="218">
@@ -6369,7 +6366,7 @@
         <v>10</v>
       </c>
       <c r="F218" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="219">
@@ -6389,7 +6386,7 @@
         <v>10</v>
       </c>
       <c r="F219" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="220">
@@ -6409,7 +6406,7 @@
         <v>10</v>
       </c>
       <c r="F220" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="221">
@@ -6429,7 +6426,7 @@
         <v>10</v>
       </c>
       <c r="F221" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="222">
@@ -6449,7 +6446,7 @@
         <v>10</v>
       </c>
       <c r="F222" t="n" s="0">
-        <v>14.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="223">
@@ -6469,7 +6466,7 @@
         <v>10</v>
       </c>
       <c r="F223" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="224">
@@ -6489,7 +6486,7 @@
         <v>10</v>
       </c>
       <c r="F224" t="n" s="0">
-        <v>18.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="225">
@@ -6509,7 +6506,7 @@
         <v>10</v>
       </c>
       <c r="F225" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="226">
@@ -6529,7 +6526,7 @@
         <v>10</v>
       </c>
       <c r="F226" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="227">
@@ -6549,7 +6546,7 @@
         <v>10</v>
       </c>
       <c r="F227" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="228">
@@ -6569,7 +6566,7 @@
         <v>10</v>
       </c>
       <c r="F228" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="229">
@@ -6589,7 +6586,7 @@
         <v>10</v>
       </c>
       <c r="F229" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="230">
@@ -6609,7 +6606,7 @@
         <v>10</v>
       </c>
       <c r="F230" t="n" s="0">
-        <v>18.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="231">
@@ -6629,7 +6626,7 @@
         <v>10</v>
       </c>
       <c r="F231" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="232">
@@ -6649,7 +6646,7 @@
         <v>10</v>
       </c>
       <c r="F232" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="233">
@@ -6669,7 +6666,7 @@
         <v>10</v>
       </c>
       <c r="F233" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="234">
@@ -6689,7 +6686,7 @@
         <v>10</v>
       </c>
       <c r="F234" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="235">
@@ -6709,7 +6706,7 @@
         <v>10</v>
       </c>
       <c r="F235" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="236">
@@ -6729,7 +6726,7 @@
         <v>10</v>
       </c>
       <c r="F236" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="237">
@@ -6749,7 +6746,7 @@
         <v>10</v>
       </c>
       <c r="F237" t="n" s="0">
-        <v>19.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="238">
@@ -6769,7 +6766,7 @@
         <v>10</v>
       </c>
       <c r="F238" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="239">
@@ -6789,7 +6786,7 @@
         <v>10</v>
       </c>
       <c r="F239" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="240">
@@ -6809,7 +6806,7 @@
         <v>10</v>
       </c>
       <c r="F240" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="241">
@@ -6829,7 +6826,7 @@
         <v>10</v>
       </c>
       <c r="F241" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="242">
@@ -6849,7 +6846,7 @@
         <v>10</v>
       </c>
       <c r="F242" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="243">
@@ -6869,7 +6866,7 @@
         <v>10</v>
       </c>
       <c r="F243" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="244">
@@ -6889,7 +6886,7 @@
         <v>10</v>
       </c>
       <c r="F244" t="n" s="0">
-        <v>18.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="245">
@@ -6909,7 +6906,7 @@
         <v>10</v>
       </c>
       <c r="F245" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="246">
@@ -6929,7 +6926,7 @@
         <v>10</v>
       </c>
       <c r="F246" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="247">
@@ -6949,7 +6946,7 @@
         <v>10</v>
       </c>
       <c r="F247" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="248">
@@ -6969,7 +6966,7 @@
         <v>10</v>
       </c>
       <c r="F248" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="249">
@@ -6989,7 +6986,7 @@
         <v>10</v>
       </c>
       <c r="F249" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="250">
@@ -7009,7 +7006,7 @@
         <v>10</v>
       </c>
       <c r="F250" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="251">
@@ -7029,7 +7026,7 @@
         <v>10</v>
       </c>
       <c r="F251" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="252">
@@ -7049,7 +7046,7 @@
         <v>10</v>
       </c>
       <c r="F252" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="253">
@@ -7069,7 +7066,7 @@
         <v>10</v>
       </c>
       <c r="F253" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="254">
@@ -7089,7 +7086,7 @@
         <v>10</v>
       </c>
       <c r="F254" t="n" s="0">
-        <v>21.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="255">
@@ -7109,7 +7106,7 @@
         <v>10</v>
       </c>
       <c r="F255" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="256">
@@ -7129,7 +7126,7 @@
         <v>10</v>
       </c>
       <c r="F256" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="257">
@@ -7149,7 +7146,7 @@
         <v>10</v>
       </c>
       <c r="F257" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="258">
@@ -7169,7 +7166,7 @@
         <v>10</v>
       </c>
       <c r="F258" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="259">
@@ -7189,7 +7186,7 @@
         <v>10</v>
       </c>
       <c r="F259" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="260">
@@ -7209,7 +7206,7 @@
         <v>10</v>
       </c>
       <c r="F260" t="n" s="0">
-        <v>19.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="261">
@@ -7229,7 +7226,7 @@
         <v>10</v>
       </c>
       <c r="F261" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="262">
@@ -7249,7 +7246,7 @@
         <v>10</v>
       </c>
       <c r="F262" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="263">
@@ -7269,7 +7266,7 @@
         <v>10</v>
       </c>
       <c r="F263" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="264">
@@ -7289,7 +7286,7 @@
         <v>10</v>
       </c>
       <c r="F264" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="265">
@@ -7309,7 +7306,7 @@
         <v>10</v>
       </c>
       <c r="F265" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="266">
@@ -7329,7 +7326,7 @@
         <v>10</v>
       </c>
       <c r="F266" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="267">
@@ -7349,7 +7346,7 @@
         <v>10</v>
       </c>
       <c r="F267" t="n" s="0">
-        <v>18.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="268">
@@ -7369,7 +7366,7 @@
         <v>10</v>
       </c>
       <c r="F268" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="269">
@@ -7389,7 +7386,7 @@
         <v>10</v>
       </c>
       <c r="F269" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="270">
@@ -7409,7 +7406,7 @@
         <v>10</v>
       </c>
       <c r="F270" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="271">
@@ -7429,7 +7426,7 @@
         <v>10</v>
       </c>
       <c r="F271" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="272">
@@ -7449,7 +7446,7 @@
         <v>10</v>
       </c>
       <c r="F272" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="273">
@@ -7469,7 +7466,7 @@
         <v>10</v>
       </c>
       <c r="F273" t="n" s="0">
-        <v>18.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="274">
@@ -7489,7 +7486,7 @@
         <v>10</v>
       </c>
       <c r="F274" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="275">
@@ -7509,7 +7506,7 @@
         <v>10</v>
       </c>
       <c r="F275" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="276">
@@ -7529,7 +7526,7 @@
         <v>10</v>
       </c>
       <c r="F276" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="277">
@@ -7549,7 +7546,7 @@
         <v>10</v>
       </c>
       <c r="F277" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="278">
@@ -7569,7 +7566,7 @@
         <v>10</v>
       </c>
       <c r="F278" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="279">
@@ -7589,7 +7586,7 @@
         <v>10</v>
       </c>
       <c r="F279" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="280">
@@ -7609,7 +7606,7 @@
         <v>10</v>
       </c>
       <c r="F280" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="281">
@@ -7629,7 +7626,7 @@
         <v>10</v>
       </c>
       <c r="F281" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="282">
@@ -7649,7 +7646,7 @@
         <v>10</v>
       </c>
       <c r="F282" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="283">
@@ -7669,7 +7666,7 @@
         <v>10</v>
       </c>
       <c r="F283" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="284">
@@ -7689,7 +7686,7 @@
         <v>10</v>
       </c>
       <c r="F284" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="285">
@@ -7709,7 +7706,7 @@
         <v>10</v>
       </c>
       <c r="F285" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="286">
@@ -7729,7 +7726,7 @@
         <v>10</v>
       </c>
       <c r="F286" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="287">
@@ -7749,7 +7746,7 @@
         <v>10</v>
       </c>
       <c r="F287" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="288">
@@ -7769,7 +7766,7 @@
         <v>10</v>
       </c>
       <c r="F288" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="289">
@@ -7789,7 +7786,7 @@
         <v>10</v>
       </c>
       <c r="F289" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="290">
@@ -7809,7 +7806,7 @@
         <v>10</v>
       </c>
       <c r="F290" t="n" s="0">
-        <v>19.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="291">
@@ -7829,7 +7826,7 @@
         <v>10</v>
       </c>
       <c r="F291" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="292">
@@ -7849,7 +7846,7 @@
         <v>10</v>
       </c>
       <c r="F292" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="293">
@@ -7869,7 +7866,7 @@
         <v>10</v>
       </c>
       <c r="F293" t="n" s="0">
-        <v>18.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="294">
@@ -7889,7 +7886,7 @@
         <v>10</v>
       </c>
       <c r="F294" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="295">
@@ -7909,7 +7906,7 @@
         <v>10</v>
       </c>
       <c r="F295" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="296">
@@ -7929,7 +7926,7 @@
         <v>10</v>
       </c>
       <c r="F296" t="n" s="0">
-        <v>18.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="297">
@@ -7949,7 +7946,7 @@
         <v>10</v>
       </c>
       <c r="F297" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="298">
@@ -7969,7 +7966,7 @@
         <v>10</v>
       </c>
       <c r="F298" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="299">
@@ -7989,7 +7986,7 @@
         <v>10</v>
       </c>
       <c r="F299" t="n" s="0">
-        <v>18.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="300">
@@ -8009,7 +8006,7 @@
         <v>10</v>
       </c>
       <c r="F300" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="301">
@@ -8029,7 +8026,7 @@
         <v>10</v>
       </c>
       <c r="F301" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
   </sheetData>
@@ -8087,7 +8084,7 @@
         <v>10</v>
       </c>
       <c r="F2" t="n" s="0">
-        <v>30.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="3">
@@ -8107,7 +8104,7 @@
         <v>10</v>
       </c>
       <c r="F3" t="n" s="0">
-        <v>14.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="4">
@@ -8127,7 +8124,7 @@
         <v>10</v>
       </c>
       <c r="F4" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="5">
@@ -8147,7 +8144,7 @@
         <v>10</v>
       </c>
       <c r="F5" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="6">
@@ -8167,7 +8164,7 @@
         <v>10</v>
       </c>
       <c r="F6" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="7">
@@ -8187,7 +8184,7 @@
         <v>10</v>
       </c>
       <c r="F7" t="n" s="0">
-        <v>14.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="8">
@@ -8207,7 +8204,7 @@
         <v>10</v>
       </c>
       <c r="F8" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="9">
@@ -8227,7 +8224,7 @@
         <v>10</v>
       </c>
       <c r="F9" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="10">
@@ -8247,7 +8244,7 @@
         <v>10</v>
       </c>
       <c r="F10" t="n" s="0">
-        <v>20.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="11">
@@ -8267,7 +8264,7 @@
         <v>10</v>
       </c>
       <c r="F11" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="12">
@@ -8287,7 +8284,7 @@
         <v>10</v>
       </c>
       <c r="F12" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="13">
@@ -8307,7 +8304,7 @@
         <v>10</v>
       </c>
       <c r="F13" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="14">
@@ -8327,7 +8324,7 @@
         <v>10</v>
       </c>
       <c r="F14" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="15">
@@ -8347,7 +8344,7 @@
         <v>10</v>
       </c>
       <c r="F15" t="n" s="0">
-        <v>14.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="16">
@@ -8367,7 +8364,7 @@
         <v>10</v>
       </c>
       <c r="F16" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="17">
@@ -8387,7 +8384,7 @@
         <v>10</v>
       </c>
       <c r="F17" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="18">
@@ -8407,7 +8404,7 @@
         <v>10</v>
       </c>
       <c r="F18" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="19">
@@ -8427,7 +8424,7 @@
         <v>10</v>
       </c>
       <c r="F19" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="20">
@@ -8447,7 +8444,7 @@
         <v>10</v>
       </c>
       <c r="F20" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="21">
@@ -8467,7 +8464,7 @@
         <v>10</v>
       </c>
       <c r="F21" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="22">
@@ -8487,7 +8484,7 @@
         <v>10</v>
       </c>
       <c r="F22" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="23">
@@ -8507,7 +8504,7 @@
         <v>10</v>
       </c>
       <c r="F23" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="24">
@@ -8527,7 +8524,7 @@
         <v>10</v>
       </c>
       <c r="F24" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="25">
@@ -8547,7 +8544,7 @@
         <v>10</v>
       </c>
       <c r="F25" t="n" s="0">
-        <v>11.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="26">
@@ -8567,7 +8564,7 @@
         <v>10</v>
       </c>
       <c r="F26" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="27">
@@ -8587,7 +8584,7 @@
         <v>10</v>
       </c>
       <c r="F27" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="28">
@@ -8607,7 +8604,7 @@
         <v>10</v>
       </c>
       <c r="F28" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="29">
@@ -8627,7 +8624,7 @@
         <v>10</v>
       </c>
       <c r="F29" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="30">
@@ -8647,7 +8644,7 @@
         <v>10</v>
       </c>
       <c r="F30" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="31">
@@ -8667,7 +8664,7 @@
         <v>10</v>
       </c>
       <c r="F31" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="32">
@@ -8687,7 +8684,7 @@
         <v>10</v>
       </c>
       <c r="F32" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="33">
@@ -8707,7 +8704,7 @@
         <v>10</v>
       </c>
       <c r="F33" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="34">
@@ -8727,7 +8724,7 @@
         <v>10</v>
       </c>
       <c r="F34" t="n" s="0">
-        <v>14.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="35">
@@ -8747,7 +8744,7 @@
         <v>10</v>
       </c>
       <c r="F35" t="n" s="0">
-        <v>14.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="36">
@@ -8767,7 +8764,7 @@
         <v>10</v>
       </c>
       <c r="F36" t="n" s="0">
-        <v>14.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="37">
@@ -8787,7 +8784,7 @@
         <v>10</v>
       </c>
       <c r="F37" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="38">
@@ -8807,7 +8804,7 @@
         <v>10</v>
       </c>
       <c r="F38" t="n" s="0">
-        <v>14.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="39">
@@ -8827,7 +8824,7 @@
         <v>10</v>
       </c>
       <c r="F39" t="n" s="0">
-        <v>14.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="40">
@@ -8847,7 +8844,7 @@
         <v>10</v>
       </c>
       <c r="F40" t="n" s="0">
-        <v>21.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="41">
@@ -8867,7 +8864,7 @@
         <v>10</v>
       </c>
       <c r="F41" t="n" s="0">
-        <v>26.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="42">
@@ -8887,7 +8884,7 @@
         <v>10</v>
       </c>
       <c r="F42" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="43">
@@ -8907,7 +8904,7 @@
         <v>10</v>
       </c>
       <c r="F43" t="n" s="0">
-        <v>18.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="44">
@@ -8927,7 +8924,7 @@
         <v>10</v>
       </c>
       <c r="F44" t="n" s="0">
-        <v>21.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="45">
@@ -8947,7 +8944,7 @@
         <v>10</v>
       </c>
       <c r="F45" t="n" s="0">
-        <v>25.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="46">
@@ -8967,7 +8964,7 @@
         <v>10</v>
       </c>
       <c r="F46" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="47">
@@ -8987,7 +8984,7 @@
         <v>10</v>
       </c>
       <c r="F47" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="48">
@@ -9007,7 +9004,7 @@
         <v>10</v>
       </c>
       <c r="F48" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="49">
@@ -9027,7 +9024,7 @@
         <v>10</v>
       </c>
       <c r="F49" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="50">
@@ -9047,7 +9044,7 @@
         <v>10</v>
       </c>
       <c r="F50" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="51">
@@ -9067,7 +9064,7 @@
         <v>10</v>
       </c>
       <c r="F51" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="52">
@@ -9087,7 +9084,7 @@
         <v>10</v>
       </c>
       <c r="F52" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="53">
@@ -9107,7 +9104,7 @@
         <v>10</v>
       </c>
       <c r="F53" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="54">
@@ -9127,7 +9124,7 @@
         <v>10</v>
       </c>
       <c r="F54" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="55">
@@ -9147,7 +9144,7 @@
         <v>10</v>
       </c>
       <c r="F55" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="56">
@@ -9167,7 +9164,7 @@
         <v>10</v>
       </c>
       <c r="F56" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="57">
@@ -9187,7 +9184,7 @@
         <v>10</v>
       </c>
       <c r="F57" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="58">
@@ -9207,7 +9204,7 @@
         <v>10</v>
       </c>
       <c r="F58" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="59">
@@ -9227,7 +9224,7 @@
         <v>10</v>
       </c>
       <c r="F59" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="60">
@@ -9247,7 +9244,7 @@
         <v>10</v>
       </c>
       <c r="F60" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="61">
@@ -9267,7 +9264,7 @@
         <v>10</v>
       </c>
       <c r="F61" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="62">
@@ -9287,7 +9284,7 @@
         <v>10</v>
       </c>
       <c r="F62" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="63">
@@ -9307,7 +9304,7 @@
         <v>10</v>
       </c>
       <c r="F63" t="n" s="0">
-        <v>19.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="64">
@@ -9327,7 +9324,7 @@
         <v>10</v>
       </c>
       <c r="F64" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="65">
@@ -9347,7 +9344,7 @@
         <v>10</v>
       </c>
       <c r="F65" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="66">
@@ -9367,7 +9364,7 @@
         <v>10</v>
       </c>
       <c r="F66" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="67">
@@ -9387,7 +9384,7 @@
         <v>10</v>
       </c>
       <c r="F67" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="68">
@@ -9407,7 +9404,7 @@
         <v>10</v>
       </c>
       <c r="F68" t="n" s="0">
-        <v>23.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="69">
@@ -9427,7 +9424,7 @@
         <v>10</v>
       </c>
       <c r="F69" t="n" s="0">
-        <v>12.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="70">
@@ -9447,7 +9444,7 @@
         <v>10</v>
       </c>
       <c r="F70" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="71">
@@ -9467,7 +9464,7 @@
         <v>10</v>
       </c>
       <c r="F71" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="72">
@@ -9487,7 +9484,7 @@
         <v>10</v>
       </c>
       <c r="F72" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="73">
@@ -9507,7 +9504,7 @@
         <v>10</v>
       </c>
       <c r="F73" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="74">
@@ -9527,7 +9524,7 @@
         <v>10</v>
       </c>
       <c r="F74" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="75">
@@ -9547,7 +9544,7 @@
         <v>10</v>
       </c>
       <c r="F75" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="76">
@@ -9567,7 +9564,7 @@
         <v>10</v>
       </c>
       <c r="F76" t="n" s="0">
-        <v>14.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="77">
@@ -9587,7 +9584,7 @@
         <v>10</v>
       </c>
       <c r="F77" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="78">
@@ -9607,7 +9604,7 @@
         <v>10</v>
       </c>
       <c r="F78" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="79">
@@ -9627,7 +9624,7 @@
         <v>10</v>
       </c>
       <c r="F79" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="80">
@@ -9647,7 +9644,7 @@
         <v>10</v>
       </c>
       <c r="F80" t="n" s="0">
-        <v>19.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="81">
@@ -9667,7 +9664,7 @@
         <v>10</v>
       </c>
       <c r="F81" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="82">
@@ -9687,7 +9684,7 @@
         <v>10</v>
       </c>
       <c r="F82" t="n" s="0">
-        <v>19.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="83">
@@ -9707,7 +9704,7 @@
         <v>10</v>
       </c>
       <c r="F83" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="84">
@@ -9727,7 +9724,7 @@
         <v>10</v>
       </c>
       <c r="F84" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="85">
@@ -9747,7 +9744,7 @@
         <v>10</v>
       </c>
       <c r="F85" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="86">
@@ -9767,7 +9764,7 @@
         <v>10</v>
       </c>
       <c r="F86" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="87">
@@ -9787,7 +9784,7 @@
         <v>10</v>
       </c>
       <c r="F87" t="n" s="0">
-        <v>18.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="88">
@@ -9807,7 +9804,7 @@
         <v>10</v>
       </c>
       <c r="F88" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="89">
@@ -9827,7 +9824,7 @@
         <v>10</v>
       </c>
       <c r="F89" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="90">
@@ -9847,7 +9844,7 @@
         <v>10</v>
       </c>
       <c r="F90" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="91">
@@ -9867,7 +9864,7 @@
         <v>10</v>
       </c>
       <c r="F91" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="92">
@@ -9887,7 +9884,7 @@
         <v>10</v>
       </c>
       <c r="F92" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="93">
@@ -9907,7 +9904,7 @@
         <v>10</v>
       </c>
       <c r="F93" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="94">
@@ -9927,7 +9924,7 @@
         <v>10</v>
       </c>
       <c r="F94" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="95">
@@ -9947,7 +9944,7 @@
         <v>10</v>
       </c>
       <c r="F95" t="n" s="0">
-        <v>19.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="96">
@@ -9967,7 +9964,7 @@
         <v>10</v>
       </c>
       <c r="F96" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="97">
@@ -9987,7 +9984,7 @@
         <v>10</v>
       </c>
       <c r="F97" t="n" s="0">
-        <v>14.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="98">
@@ -10007,7 +10004,7 @@
         <v>10</v>
       </c>
       <c r="F98" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="99">
@@ -10027,7 +10024,7 @@
         <v>10</v>
       </c>
       <c r="F99" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="100">
@@ -10047,7 +10044,7 @@
         <v>10</v>
       </c>
       <c r="F100" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="101">
@@ -10067,7 +10064,7 @@
         <v>10</v>
       </c>
       <c r="F101" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="102">
@@ -10087,7 +10084,7 @@
         <v>10</v>
       </c>
       <c r="F102" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="103">
@@ -10107,7 +10104,7 @@
         <v>10</v>
       </c>
       <c r="F103" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="104">
@@ -10127,7 +10124,7 @@
         <v>10</v>
       </c>
       <c r="F104" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="105">
@@ -10147,7 +10144,7 @@
         <v>10</v>
       </c>
       <c r="F105" t="n" s="0">
-        <v>18.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="106">
@@ -10167,7 +10164,7 @@
         <v>10</v>
       </c>
       <c r="F106" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="107">
@@ -10187,7 +10184,7 @@
         <v>10</v>
       </c>
       <c r="F107" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="108">
@@ -10207,7 +10204,7 @@
         <v>10</v>
       </c>
       <c r="F108" t="n" s="0">
-        <v>14.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="109">
@@ -10227,7 +10224,7 @@
         <v>10</v>
       </c>
       <c r="F109" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="110">
@@ -10247,7 +10244,7 @@
         <v>10</v>
       </c>
       <c r="F110" t="n" s="0">
-        <v>19.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="111">
@@ -10267,7 +10264,7 @@
         <v>10</v>
       </c>
       <c r="F111" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="112">
@@ -10287,7 +10284,7 @@
         <v>10</v>
       </c>
       <c r="F112" t="n" s="0">
-        <v>14.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="113">
@@ -10307,7 +10304,7 @@
         <v>10</v>
       </c>
       <c r="F113" t="n" s="0">
-        <v>18.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="114">
@@ -10327,7 +10324,7 @@
         <v>10</v>
       </c>
       <c r="F114" t="n" s="0">
-        <v>14.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="115">
@@ -10347,7 +10344,7 @@
         <v>10</v>
       </c>
       <c r="F115" t="n" s="0">
-        <v>18.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="116">
@@ -10367,7 +10364,7 @@
         <v>10</v>
       </c>
       <c r="F116" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="117">
@@ -10387,7 +10384,7 @@
         <v>10</v>
       </c>
       <c r="F117" t="n" s="0">
-        <v>18.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="118">
@@ -10407,7 +10404,7 @@
         <v>10</v>
       </c>
       <c r="F118" t="n" s="0">
-        <v>14.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="119">
@@ -10427,7 +10424,7 @@
         <v>10</v>
       </c>
       <c r="F119" t="n" s="0">
-        <v>18.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="120">
@@ -10447,7 +10444,7 @@
         <v>10</v>
       </c>
       <c r="F120" t="n" s="0">
-        <v>14.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="121">
@@ -10467,7 +10464,7 @@
         <v>10</v>
       </c>
       <c r="F121" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="122">
@@ -10487,7 +10484,7 @@
         <v>10</v>
       </c>
       <c r="F122" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="123">
@@ -10507,7 +10504,7 @@
         <v>10</v>
       </c>
       <c r="F123" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="124">
@@ -10527,7 +10524,7 @@
         <v>10</v>
       </c>
       <c r="F124" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="125">
@@ -10547,7 +10544,7 @@
         <v>10</v>
       </c>
       <c r="F125" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="126">
@@ -10567,7 +10564,7 @@
         <v>10</v>
       </c>
       <c r="F126" t="n" s="0">
-        <v>13.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="127">
@@ -10587,7 +10584,7 @@
         <v>10</v>
       </c>
       <c r="F127" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="128">
@@ -10607,7 +10604,7 @@
         <v>10</v>
       </c>
       <c r="F128" t="n" s="0">
-        <v>18.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="129">
@@ -10627,7 +10624,7 @@
         <v>10</v>
       </c>
       <c r="F129" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="130">
@@ -10647,7 +10644,7 @@
         <v>10</v>
       </c>
       <c r="F130" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="131">
@@ -10667,7 +10664,7 @@
         <v>10</v>
       </c>
       <c r="F131" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="132">
@@ -10687,7 +10684,7 @@
         <v>10</v>
       </c>
       <c r="F132" t="n" s="0">
-        <v>14.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="133">
@@ -10707,7 +10704,7 @@
         <v>10</v>
       </c>
       <c r="F133" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="134">
@@ -10727,7 +10724,7 @@
         <v>10</v>
       </c>
       <c r="F134" t="n" s="0">
-        <v>14.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="135">
@@ -10747,7 +10744,7 @@
         <v>10</v>
       </c>
       <c r="F135" t="n" s="0">
-        <v>19.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="136">
@@ -10767,7 +10764,7 @@
         <v>10</v>
       </c>
       <c r="F136" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="137">
@@ -10787,7 +10784,7 @@
         <v>10</v>
       </c>
       <c r="F137" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="138">
@@ -10807,7 +10804,7 @@
         <v>10</v>
       </c>
       <c r="F138" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="139">
@@ -10827,7 +10824,7 @@
         <v>10</v>
       </c>
       <c r="F139" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="140">
@@ -10847,7 +10844,7 @@
         <v>10</v>
       </c>
       <c r="F140" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="141">
@@ -10867,7 +10864,7 @@
         <v>10</v>
       </c>
       <c r="F141" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="142">
@@ -10887,7 +10884,7 @@
         <v>10</v>
       </c>
       <c r="F142" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="143">
@@ -10907,7 +10904,7 @@
         <v>10</v>
       </c>
       <c r="F143" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="144">
@@ -10927,7 +10924,7 @@
         <v>10</v>
       </c>
       <c r="F144" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="145">
@@ -10947,7 +10944,7 @@
         <v>10</v>
       </c>
       <c r="F145" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="146">
@@ -10967,7 +10964,7 @@
         <v>10</v>
       </c>
       <c r="F146" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="147">
@@ -10987,7 +10984,7 @@
         <v>10</v>
       </c>
       <c r="F147" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="148">
@@ -11007,7 +11004,7 @@
         <v>10</v>
       </c>
       <c r="F148" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="149">
@@ -11027,7 +11024,7 @@
         <v>10</v>
       </c>
       <c r="F149" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="150">
@@ -11047,7 +11044,7 @@
         <v>10</v>
       </c>
       <c r="F150" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="151">
@@ -11067,7 +11064,7 @@
         <v>10</v>
       </c>
       <c r="F151" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="152">
@@ -11087,7 +11084,7 @@
         <v>10</v>
       </c>
       <c r="F152" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="153">
@@ -11107,7 +11104,7 @@
         <v>10</v>
       </c>
       <c r="F153" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="154">
@@ -11127,7 +11124,7 @@
         <v>10</v>
       </c>
       <c r="F154" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="155">
@@ -11147,7 +11144,7 @@
         <v>10</v>
       </c>
       <c r="F155" t="n" s="0">
-        <v>18.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="156">
@@ -11167,7 +11164,7 @@
         <v>10</v>
       </c>
       <c r="F156" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="157">
@@ -11187,7 +11184,7 @@
         <v>10</v>
       </c>
       <c r="F157" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="158">
@@ -11207,7 +11204,7 @@
         <v>10</v>
       </c>
       <c r="F158" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="159">
@@ -11227,7 +11224,7 @@
         <v>10</v>
       </c>
       <c r="F159" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="160">
@@ -11247,7 +11244,7 @@
         <v>10</v>
       </c>
       <c r="F160" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="161">
@@ -11267,7 +11264,7 @@
         <v>10</v>
       </c>
       <c r="F161" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="162">
@@ -11287,7 +11284,7 @@
         <v>10</v>
       </c>
       <c r="F162" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="163">
@@ -11307,7 +11304,7 @@
         <v>10</v>
       </c>
       <c r="F163" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="164">
@@ -11327,7 +11324,7 @@
         <v>10</v>
       </c>
       <c r="F164" t="n" s="0">
-        <v>19.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="165">
@@ -11347,7 +11344,7 @@
         <v>10</v>
       </c>
       <c r="F165" t="n" s="0">
-        <v>14.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="166">
@@ -11367,7 +11364,7 @@
         <v>10</v>
       </c>
       <c r="F166" t="n" s="0">
-        <v>19.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="167">
@@ -11387,7 +11384,7 @@
         <v>10</v>
       </c>
       <c r="F167" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="168">
@@ -11407,7 +11404,7 @@
         <v>10</v>
       </c>
       <c r="F168" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="169">
@@ -11427,7 +11424,7 @@
         <v>10</v>
       </c>
       <c r="F169" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="170">
@@ -11447,7 +11444,7 @@
         <v>10</v>
       </c>
       <c r="F170" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="171">
@@ -11467,7 +11464,7 @@
         <v>10</v>
       </c>
       <c r="F171" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="172">
@@ -11487,7 +11484,7 @@
         <v>10</v>
       </c>
       <c r="F172" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="173">
@@ -11507,7 +11504,7 @@
         <v>10</v>
       </c>
       <c r="F173" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="174">
@@ -11527,7 +11524,7 @@
         <v>10</v>
       </c>
       <c r="F174" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="175">
@@ -11547,7 +11544,7 @@
         <v>10</v>
       </c>
       <c r="F175" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="176">
@@ -11567,7 +11564,7 @@
         <v>10</v>
       </c>
       <c r="F176" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="177">
@@ -11587,7 +11584,7 @@
         <v>10</v>
       </c>
       <c r="F177" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="178">
@@ -11607,7 +11604,7 @@
         <v>10</v>
       </c>
       <c r="F178" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="179">
@@ -11627,7 +11624,7 @@
         <v>10</v>
       </c>
       <c r="F179" t="n" s="0">
-        <v>18.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="180">
@@ -11647,7 +11644,7 @@
         <v>10</v>
       </c>
       <c r="F180" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="181">
@@ -11667,7 +11664,7 @@
         <v>10</v>
       </c>
       <c r="F181" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="182">
@@ -11687,7 +11684,7 @@
         <v>10</v>
       </c>
       <c r="F182" t="n" s="0">
-        <v>18.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="183">
@@ -11707,7 +11704,7 @@
         <v>10</v>
       </c>
       <c r="F183" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="184">
@@ -11727,7 +11724,7 @@
         <v>10</v>
       </c>
       <c r="F184" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="185">
@@ -11747,7 +11744,7 @@
         <v>10</v>
       </c>
       <c r="F185" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="186">
@@ -11767,7 +11764,7 @@
         <v>10</v>
       </c>
       <c r="F186" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="187">
@@ -11787,7 +11784,7 @@
         <v>10</v>
       </c>
       <c r="F187" t="n" s="0">
-        <v>18.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="188">
@@ -11807,7 +11804,7 @@
         <v>10</v>
       </c>
       <c r="F188" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="189">
@@ -11827,7 +11824,7 @@
         <v>10</v>
       </c>
       <c r="F189" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="190">
@@ -11847,7 +11844,7 @@
         <v>10</v>
       </c>
       <c r="F190" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="191">
@@ -11867,7 +11864,7 @@
         <v>10</v>
       </c>
       <c r="F191" t="n" s="0">
-        <v>18.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="192">
@@ -11887,7 +11884,7 @@
         <v>10</v>
       </c>
       <c r="F192" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="193">
@@ -11907,7 +11904,7 @@
         <v>10</v>
       </c>
       <c r="F193" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="194">
@@ -11927,7 +11924,7 @@
         <v>10</v>
       </c>
       <c r="F194" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="195">
@@ -11947,7 +11944,7 @@
         <v>10</v>
       </c>
       <c r="F195" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="196">
@@ -11967,7 +11964,7 @@
         <v>10</v>
       </c>
       <c r="F196" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="197">
@@ -11987,7 +11984,7 @@
         <v>10</v>
       </c>
       <c r="F197" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="198">
@@ -12007,7 +12004,7 @@
         <v>10</v>
       </c>
       <c r="F198" t="n" s="0">
-        <v>18.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="199">
@@ -12027,7 +12024,7 @@
         <v>10</v>
       </c>
       <c r="F199" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="200">
@@ -12047,7 +12044,7 @@
         <v>10</v>
       </c>
       <c r="F200" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="201">
@@ -12067,7 +12064,7 @@
         <v>10</v>
       </c>
       <c r="F201" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="202">
@@ -12087,7 +12084,7 @@
         <v>10</v>
       </c>
       <c r="F202" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="203">
@@ -12107,7 +12104,7 @@
         <v>10</v>
       </c>
       <c r="F203" t="n" s="0">
-        <v>18.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="204">
@@ -12127,7 +12124,7 @@
         <v>10</v>
       </c>
       <c r="F204" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="205">
@@ -12147,7 +12144,7 @@
         <v>10</v>
       </c>
       <c r="F205" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="206">
@@ -12167,7 +12164,7 @@
         <v>10</v>
       </c>
       <c r="F206" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="207">
@@ -12187,7 +12184,7 @@
         <v>10</v>
       </c>
       <c r="F207" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="208">
@@ -12207,7 +12204,7 @@
         <v>10</v>
       </c>
       <c r="F208" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="209">
@@ -12227,7 +12224,7 @@
         <v>10</v>
       </c>
       <c r="F209" t="n" s="0">
-        <v>18.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="210">
@@ -12247,7 +12244,7 @@
         <v>10</v>
       </c>
       <c r="F210" t="n" s="0">
-        <v>14.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="211">
@@ -12267,7 +12264,7 @@
         <v>10</v>
       </c>
       <c r="F211" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="212">
@@ -12287,7 +12284,7 @@
         <v>10</v>
       </c>
       <c r="F212" t="n" s="0">
-        <v>19.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="213">
@@ -12307,7 +12304,7 @@
         <v>10</v>
       </c>
       <c r="F213" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="214">
@@ -12327,7 +12324,7 @@
         <v>10</v>
       </c>
       <c r="F214" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="215">
@@ -12347,7 +12344,7 @@
         <v>10</v>
       </c>
       <c r="F215" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="216">
@@ -12367,7 +12364,7 @@
         <v>10</v>
       </c>
       <c r="F216" t="n" s="0">
-        <v>14.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="217">
@@ -12387,7 +12384,7 @@
         <v>10</v>
       </c>
       <c r="F217" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="218">
@@ -12407,7 +12404,7 @@
         <v>10</v>
       </c>
       <c r="F218" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="219">
@@ -12427,7 +12424,7 @@
         <v>10</v>
       </c>
       <c r="F219" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="220">
@@ -12447,7 +12444,7 @@
         <v>10</v>
       </c>
       <c r="F220" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="221">
@@ -12467,7 +12464,7 @@
         <v>10</v>
       </c>
       <c r="F221" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="222">
@@ -12487,7 +12484,7 @@
         <v>10</v>
       </c>
       <c r="F222" t="n" s="0">
-        <v>14.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="223">
@@ -12507,7 +12504,7 @@
         <v>10</v>
       </c>
       <c r="F223" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="224">
@@ -12527,7 +12524,7 @@
         <v>10</v>
       </c>
       <c r="F224" t="n" s="0">
-        <v>18.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="225">
@@ -12547,7 +12544,7 @@
         <v>10</v>
       </c>
       <c r="F225" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="226">
@@ -12567,7 +12564,7 @@
         <v>10</v>
       </c>
       <c r="F226" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="227">
@@ -12587,7 +12584,7 @@
         <v>10</v>
       </c>
       <c r="F227" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="228">
@@ -12607,7 +12604,7 @@
         <v>10</v>
       </c>
       <c r="F228" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="229">
@@ -12627,7 +12624,7 @@
         <v>10</v>
       </c>
       <c r="F229" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="230">
@@ -12647,7 +12644,7 @@
         <v>10</v>
       </c>
       <c r="F230" t="n" s="0">
-        <v>18.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="231">
@@ -12667,7 +12664,7 @@
         <v>10</v>
       </c>
       <c r="F231" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="232">
@@ -12687,7 +12684,7 @@
         <v>10</v>
       </c>
       <c r="F232" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="233">
@@ -12707,7 +12704,7 @@
         <v>10</v>
       </c>
       <c r="F233" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="234">
@@ -12727,7 +12724,7 @@
         <v>10</v>
       </c>
       <c r="F234" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="235">
@@ -12747,7 +12744,7 @@
         <v>10</v>
       </c>
       <c r="F235" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="236">
@@ -12767,7 +12764,7 @@
         <v>10</v>
       </c>
       <c r="F236" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="237">
@@ -12787,7 +12784,7 @@
         <v>10</v>
       </c>
       <c r="F237" t="n" s="0">
-        <v>19.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="238">
@@ -12807,7 +12804,7 @@
         <v>10</v>
       </c>
       <c r="F238" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="239">
@@ -12827,7 +12824,7 @@
         <v>10</v>
       </c>
       <c r="F239" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="240">
@@ -12847,7 +12844,7 @@
         <v>10</v>
       </c>
       <c r="F240" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="241">
@@ -12867,7 +12864,7 @@
         <v>10</v>
       </c>
       <c r="F241" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="242">
@@ -12887,7 +12884,7 @@
         <v>10</v>
       </c>
       <c r="F242" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="243">
@@ -12907,7 +12904,7 @@
         <v>10</v>
       </c>
       <c r="F243" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="244">
@@ -12927,7 +12924,7 @@
         <v>10</v>
       </c>
       <c r="F244" t="n" s="0">
-        <v>18.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="245">
@@ -12947,7 +12944,7 @@
         <v>10</v>
       </c>
       <c r="F245" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="246">
@@ -12967,7 +12964,7 @@
         <v>10</v>
       </c>
       <c r="F246" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="247">
@@ -12987,7 +12984,7 @@
         <v>10</v>
       </c>
       <c r="F247" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="248">
@@ -13007,7 +13004,7 @@
         <v>10</v>
       </c>
       <c r="F248" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="249">
@@ -13027,7 +13024,7 @@
         <v>10</v>
       </c>
       <c r="F249" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="250">
@@ -13047,7 +13044,7 @@
         <v>10</v>
       </c>
       <c r="F250" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="251">
@@ -13067,7 +13064,7 @@
         <v>10</v>
       </c>
       <c r="F251" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="252">
@@ -13087,7 +13084,7 @@
         <v>10</v>
       </c>
       <c r="F252" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="253">
@@ -13107,7 +13104,7 @@
         <v>10</v>
       </c>
       <c r="F253" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="254">
@@ -13127,7 +13124,7 @@
         <v>10</v>
       </c>
       <c r="F254" t="n" s="0">
-        <v>21.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="255">
@@ -13147,7 +13144,7 @@
         <v>10</v>
       </c>
       <c r="F255" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="256">
@@ -13167,7 +13164,7 @@
         <v>10</v>
       </c>
       <c r="F256" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="257">
@@ -13187,7 +13184,7 @@
         <v>10</v>
       </c>
       <c r="F257" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="258">
@@ -13207,7 +13204,7 @@
         <v>10</v>
       </c>
       <c r="F258" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="259">
@@ -13227,7 +13224,7 @@
         <v>10</v>
       </c>
       <c r="F259" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="260">
@@ -13247,7 +13244,7 @@
         <v>10</v>
       </c>
       <c r="F260" t="n" s="0">
-        <v>19.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="261">
@@ -13267,7 +13264,7 @@
         <v>10</v>
       </c>
       <c r="F261" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="262">
@@ -13287,7 +13284,7 @@
         <v>10</v>
       </c>
       <c r="F262" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="263">
@@ -13307,7 +13304,7 @@
         <v>10</v>
       </c>
       <c r="F263" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="264">
@@ -13327,7 +13324,7 @@
         <v>10</v>
       </c>
       <c r="F264" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="265">
@@ -13347,7 +13344,7 @@
         <v>10</v>
       </c>
       <c r="F265" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="266">
@@ -13367,7 +13364,7 @@
         <v>10</v>
       </c>
       <c r="F266" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="267">
@@ -13387,7 +13384,7 @@
         <v>10</v>
       </c>
       <c r="F267" t="n" s="0">
-        <v>18.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="268">
@@ -13407,7 +13404,7 @@
         <v>10</v>
       </c>
       <c r="F268" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="269">
@@ -13427,7 +13424,7 @@
         <v>10</v>
       </c>
       <c r="F269" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="270">
@@ -13447,7 +13444,7 @@
         <v>10</v>
       </c>
       <c r="F270" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="271">
@@ -13467,7 +13464,7 @@
         <v>10</v>
       </c>
       <c r="F271" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="272">
@@ -13487,7 +13484,7 @@
         <v>10</v>
       </c>
       <c r="F272" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="273">
@@ -13507,7 +13504,7 @@
         <v>10</v>
       </c>
       <c r="F273" t="n" s="0">
-        <v>18.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="274">
@@ -13527,7 +13524,7 @@
         <v>10</v>
       </c>
       <c r="F274" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="275">
@@ -13547,7 +13544,7 @@
         <v>10</v>
       </c>
       <c r="F275" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="276">
@@ -13567,7 +13564,7 @@
         <v>10</v>
       </c>
       <c r="F276" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="277">
@@ -13587,7 +13584,7 @@
         <v>10</v>
       </c>
       <c r="F277" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="278">
@@ -13607,7 +13604,7 @@
         <v>10</v>
       </c>
       <c r="F278" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="279">
@@ -13627,7 +13624,7 @@
         <v>10</v>
       </c>
       <c r="F279" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="280">
@@ -13647,7 +13644,7 @@
         <v>10</v>
       </c>
       <c r="F280" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="281">
@@ -13667,7 +13664,7 @@
         <v>10</v>
       </c>
       <c r="F281" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="282">
@@ -13687,7 +13684,7 @@
         <v>10</v>
       </c>
       <c r="F282" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="283">
@@ -13707,7 +13704,7 @@
         <v>10</v>
       </c>
       <c r="F283" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="284">
@@ -13727,7 +13724,7 @@
         <v>10</v>
       </c>
       <c r="F284" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="285">
@@ -13747,7 +13744,7 @@
         <v>10</v>
       </c>
       <c r="F285" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="286">
@@ -13767,7 +13764,7 @@
         <v>10</v>
       </c>
       <c r="F286" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="287">
@@ -13787,7 +13784,7 @@
         <v>10</v>
       </c>
       <c r="F287" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="288">
@@ -13807,7 +13804,7 @@
         <v>10</v>
       </c>
       <c r="F288" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="289">
@@ -13827,7 +13824,7 @@
         <v>10</v>
       </c>
       <c r="F289" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="290">
@@ -13847,7 +13844,7 @@
         <v>10</v>
       </c>
       <c r="F290" t="n" s="0">
-        <v>19.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="291">
@@ -13867,7 +13864,7 @@
         <v>10</v>
       </c>
       <c r="F291" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="292">
@@ -13887,7 +13884,7 @@
         <v>10</v>
       </c>
       <c r="F292" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="293">
@@ -13907,7 +13904,7 @@
         <v>10</v>
       </c>
       <c r="F293" t="n" s="0">
-        <v>18.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="294">
@@ -13927,7 +13924,7 @@
         <v>10</v>
       </c>
       <c r="F294" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="295">
@@ -13947,7 +13944,7 @@
         <v>10</v>
       </c>
       <c r="F295" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="296">
@@ -13967,7 +13964,7 @@
         <v>10</v>
       </c>
       <c r="F296" t="n" s="0">
-        <v>18.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="297">
@@ -13987,7 +13984,7 @@
         <v>10</v>
       </c>
       <c r="F297" t="n" s="0">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="298">
@@ -14007,7 +14004,7 @@
         <v>10</v>
       </c>
       <c r="F298" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="299">
@@ -14027,7 +14024,7 @@
         <v>10</v>
       </c>
       <c r="F299" t="n" s="0">
-        <v>18.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="300">
@@ -14047,7 +14044,7 @@
         <v>10</v>
       </c>
       <c r="F300" t="n" s="0">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="301">
@@ -14067,7 +14064,7 @@
         <v>10</v>
       </c>
       <c r="F301" t="n" s="0">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
   </sheetData>
@@ -14213,7 +14210,7 @@
         <v>633</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>634</v>
+        <v>629</v>
       </c>
     </row>
   </sheetData>
@@ -14235,10 +14232,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
+        <v>634</v>
+      </c>
+      <c r="B1" t="s" s="1">
         <v>635</v>
-      </c>
-      <c r="B1" t="s" s="1">
-        <v>636</v>
       </c>
       <c r="C1" t="s" s="1">
         <v>1</v>
@@ -14247,7 +14244,7 @@
         <v>3</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
   </sheetData>
@@ -14269,10 +14266,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
+        <v>637</v>
+      </c>
+      <c r="B1" t="s" s="1">
         <v>638</v>
-      </c>
-      <c r="B1" t="s" s="1">
-        <v>639</v>
       </c>
       <c r="C1" t="s" s="1">
         <v>627</v>
